--- a/survey_templates/034_nonprofit_employee_burnout_study--survey_templates.xlsx
+++ b/survey_templates/034_nonprofit_employee_burnout_study--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1858,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
